--- a/desensitizer-spring-boot/src/main/resources/test-data/赛题4-支持敏感信息脱敏的通用工具-测试数据v0.3.xlsx
+++ b/desensitizer-spring-boot/src/main/resources/test-data/赛题4-支持敏感信息脱敏的通用工具-测试数据v0.3.xlsx
@@ -9,9 +9,496 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="161">
+  <si>
+    <t>長崎県横浜市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区丹丹市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区合山市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区涛市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区六盘水市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区哈尔滨市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区济南市***</t>
+  </si>
+  <si>
+    <t>세종특별자치시 성북***</t>
+  </si>
+  <si>
+    <t>岐阜県横浜市***</t>
+  </si>
+  <si>
+    <t>西藏自治区贵阳市***</t>
+  </si>
+  <si>
+    <t>湖北省兴安盟***</t>
+  </si>
+  <si>
+    <t>세종특별자치시 송파구 백제***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区兰英市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区瑜市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区辛集市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区英市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区淑珍市***</t>
+  </si>
+  <si>
+    <t>黑龙江省宁德县沙市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区长沙市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区乌鲁木齐市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区南昌市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区贵阳市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区桂荣市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区文市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区玲市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区香港市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区娜市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区丽市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区潮州市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区颖市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区霞市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区勇市***</t>
+  </si>
+  <si>
+    <t>沖縄県横浜市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区齐齐哈尔市***</t>
+  </si>
+  <si>
+    <t>天津市超县***</t>
+  </si>
+  <si>
+    <t>台湾省明县沙市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区淑兰市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区秀英市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区拉萨市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区红市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区南京市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区莉市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区南昌市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区兰州市***</t>
+  </si>
+  <si>
+    <t>福島県***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区西宁市***</t>
+  </si>
+  <si>
+    <t>静岡県川崎市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区沈阳市***</t>
+  </si>
+  <si>
+    <t>세종특별자치시 성북구 학***</t>
+  </si>
+  <si>
+    <t>河北省辛集县沙市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区大冶市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区金凤市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区博市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区大冶市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区武汉市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区重庆市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区合山市***</t>
+  </si>
+  <si>
+    <t>熊本県***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区斌市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区兴安盟***</t>
+  </si>
+  <si>
+    <t>香港特别行政区欢市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区斌市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区沈阳市***</t>
+  </si>
+  <si>
+    <t>福井県***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区丽华市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区莉市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区雪市***</t>
+  </si>
+  <si>
+    <t>西藏自治区兴安盟***</t>
+  </si>
+  <si>
+    <t>香港特别行政区文市***</t>
+  </si>
+  <si>
+    <t>天津市深圳县***</t>
+  </si>
+  <si>
+    <t>西藏自治区阜新市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区南京市***</t>
+  </si>
+  <si>
+    <t>西藏自治区楠市***</t>
+  </si>
+  <si>
+    <t>栃木県横浜市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区合山市***</t>
+  </si>
+  <si>
+    <t>세종특별자치시 관악구 도산대***</t>
+  </si>
+  <si>
+    <t>和歌山県川崎市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区秀梅市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区婷市***</t>
+  </si>
+  <si>
+    <t>熊本県川崎市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区萍市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区沈阳市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区成市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区华市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区海口市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区阜新市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区平市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区台北市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区鹏市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区坤市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区波市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区成都市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区合肥市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区桂英市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区梧州市***</t>
+  </si>
+  <si>
+    <t>西藏自治区成市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区成都市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区龙市***</t>
+  </si>
+  <si>
+    <t>西藏自治区芳市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区冬梅市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区海口市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区洁市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区东莞市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区惠州市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区阳市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区南宁市***</t>
+  </si>
+  <si>
+    <t>西藏自治区哈尔滨市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区淑珍市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区辽阳市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区佳市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区昆明市***</t>
+  </si>
+  <si>
+    <t>河南省齐齐哈尔县***</t>
+  </si>
+  <si>
+    <t>湖北省呼和浩特县***</t>
+  </si>
+  <si>
+    <t>香港特别行政区海燕市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区马鞍山市***</t>
+  </si>
+  <si>
+    <t>西藏自治区合肥市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区丽华市***</t>
+  </si>
+  <si>
+    <t>西藏自治区台北市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区利市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区杨市***</t>
+  </si>
+  <si>
+    <t>西藏自治区玉珍市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区石家庄市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区宜都市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区志强市***</t>
+  </si>
+  <si>
+    <t>辽宁省济南县***</t>
+  </si>
+  <si>
+    <t>沖縄県***</t>
+  </si>
+  <si>
+    <t>河北省西宁县沙市***</t>
+  </si>
+  <si>
+    <t>西藏自治区淮安市***</t>
+  </si>
+  <si>
+    <t>河北省齐齐哈尔县秀英兴安盟***</t>
+  </si>
+  <si>
+    <t>佐賀県横浜市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区石家庄市***</t>
+  </si>
+  <si>
+    <t>澳门特别行政区佛山县***</t>
+  </si>
+  <si>
+    <t>台湾省惠州县***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区秀英市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区通辽市***</t>
+  </si>
+  <si>
+    <t>栃木県***</t>
+  </si>
+  <si>
+    <t>세종특별자치시 구로구 논***</t>
+  </si>
+  <si>
+    <t>天津市沈阳县***</t>
+  </si>
+  <si>
+    <t>香港特别行政区汕尾市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区南京市***</t>
+  </si>
+  <si>
+    <t>吉林省丹县***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区汕尾市***</t>
+  </si>
+  <si>
+    <t>香港特别行政区敏市***</t>
+  </si>
+  <si>
+    <t>青海省成都县沙市***</t>
+  </si>
+  <si>
+    <t>湖北省辽阳县闵行兴安盟***</t>
+  </si>
+  <si>
+    <t>山梨県横浜市***</t>
+  </si>
+  <si>
+    <t>广东省宁德县沙市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区桂芳市***</t>
+  </si>
+  <si>
+    <t>福井県横浜市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区长沙市***</t>
+  </si>
+  <si>
+    <t>甘肃省桂珍县沙市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区凤英市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区兰州市***</t>
+  </si>
+  <si>
+    <t>广西壮族自治区秀英市***</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区潜江市***</t>
+  </si>
+  <si>
+    <t>内蒙古自治区丹市***</t>
+  </si>
+  <si>
+    <t>西藏自治区关岭市***</t>
+  </si>
+  <si>
+    <t>云南省兴安盟***</t>
+  </si>
+  <si>
+    <t>香港特别行政区霞市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区燕市***</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区兴城市***</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -908,10 +1395,8 @@
           <t>622908********4685</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>長崎県横浜市港南区***</t>
-        </is>
+      <c r="K9" t="s">
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2396,10 +2881,8 @@
           <t>622908********7084</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K33" t="s">
+        <v>1</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2458,10 +2941,8 @@
           <t>622908********7183</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K34" t="s">
+        <v>2</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2644,10 +3125,8 @@
           <t>622908********7480</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K37" t="s">
+        <v>3</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2892,10 +3371,8 @@
           <t>622908********7886</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K41" t="s">
+        <v>4</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3202,10 +3679,8 @@
           <t>622908********8389</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K46" t="s">
+        <v>5</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3636,10 +4111,8 @@
           <t>622908********9080</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K53" t="s">
+        <v>6</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3884,10 +4357,8 @@
           <t>622908********9486</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>세종특별자치시 성북구***</t>
-        </is>
+      <c r="K57" t="s">
+        <v>7</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4132,10 +4603,8 @@
           <t>622908********9882</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>岐阜県横浜市金沢区***</t>
-        </is>
+      <c r="K61" t="s">
+        <v>8</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -4442,10 +4911,8 @@
           <t>622908********0385</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K66" t="s">
+        <v>9</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -5682,10 +6149,8 @@
           <t>622908********2480</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>湖北省兴安盟县***</t>
-        </is>
+      <c r="K86" t="s">
+        <v>10</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -5806,10 +6271,8 @@
           <t>622908********2688</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>세종특별자치시 송파구***</t>
-        </is>
+      <c r="K88" t="s">
+        <v>11</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5992,10 +6455,8 @@
           <t>622908********2985</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K91" t="s">
+        <v>12</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -6798,10 +7259,8 @@
           <t>622908********4288</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K104" t="s">
+        <v>13</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -6922,10 +7381,8 @@
           <t>622908********4486</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K106" t="s">
+        <v>14</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -6984,10 +7441,8 @@
           <t>622908********4585</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K107" t="s">
+        <v>15</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -7542,10 +7997,8 @@
           <t>622908********5483</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K116" t="s">
+        <v>16</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -7728,10 +8181,8 @@
           <t>622908********5780</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>黑龙江省宁德县***</t>
-        </is>
+      <c r="K119" t="s">
+        <v>17</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -7790,10 +8241,8 @@
           <t>622908********5889</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K120" t="s">
+        <v>18</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -8286,10 +8735,8 @@
           <t>622908********6689</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K128" t="s">
+        <v>19</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -8658,10 +9105,8 @@
           <t>622908********7281</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K134" t="s">
+        <v>20</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -8782,10 +9227,8 @@
           <t>622908********7489</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K136" t="s">
+        <v>21</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -11882,10 +12325,8 @@
           <t>622908********2588</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K186" t="s">
+        <v>22</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -12812,10 +13253,8 @@
           <t>622908********4089</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K201" t="s">
+        <v>23</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -13060,10 +13499,8 @@
           <t>622908********4485</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K205" t="s">
+        <v>24</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -14176,10 +14613,8 @@
           <t>622908********6282</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K223" t="s">
+        <v>25</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -14672,10 +15107,8 @@
           <t>622908********7082</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K231" t="s">
+        <v>26</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -15106,10 +15539,8 @@
           <t>622908********7785</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K238" t="s">
+        <v>27</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -15726,10 +16157,8 @@
           <t>622908********8882</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K248" t="s">
+        <v>28</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -17276,10 +17705,8 @@
           <t>622908********1381</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K273" t="s">
+        <v>29</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -17462,10 +17889,8 @@
           <t>622908********1688</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K276" t="s">
+        <v>30</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -17834,10 +18259,8 @@
           <t>622908********2280</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K282" t="s">
+        <v>31</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -18826,10 +19249,8 @@
           <t>622908********3882</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>沖縄県横浜市戸塚区***</t>
-        </is>
+      <c r="K298" t="s">
+        <v>32</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -19446,10 +19867,8 @@
           <t>622908********4880</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K308" t="s">
+        <v>33</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -20066,10 +20485,8 @@
           <t>622908********5887</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>天津市超县吉区***</t>
-        </is>
+      <c r="K318" t="s">
+        <v>34</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -20686,10 +21103,8 @@
           <t>622908********6885</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>台湾省明县***</t>
-        </is>
+      <c r="K328" t="s">
+        <v>35</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -20810,10 +21225,8 @@
           <t>622908********7081</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K330" t="s">
+        <v>36</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -21306,10 +21719,8 @@
           <t>622908********7982</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K338" t="s">
+        <v>37</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -21368,10 +21779,8 @@
           <t>622908********8089</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K339" t="s">
+        <v>38</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -21678,10 +22087,8 @@
           <t>622908********8584</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K344" t="s">
+        <v>39</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -21864,10 +22271,8 @@
           <t>622908********8881</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K347" t="s">
+        <v>40</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -22546,10 +22951,8 @@
           <t>622908********9988</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K358" t="s">
+        <v>41</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -22980,10 +23383,8 @@
           <t>622908********0689</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K365" t="s">
+        <v>42</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -23042,10 +23443,8 @@
           <t>622908********0788</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K366" t="s">
+        <v>43</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -23538,10 +23937,8 @@
           <t>622908********1588</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr">
-        <is>
-          <t>福島県新島村***</t>
-        </is>
+      <c r="K374" t="s">
+        <v>44</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -24158,10 +24555,8 @@
           <t>622908********2685</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K384" t="s">
+        <v>43</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -24406,10 +24801,8 @@
           <t>622908********3089</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K388" t="s">
+        <v>45</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -24654,10 +25047,8 @@
           <t>622908********3485</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>静岡県川崎市幸区***</t>
-        </is>
+      <c r="K392" t="s">
+        <v>46</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -25212,10 +25603,8 @@
           <t>622908********4483</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K401" t="s">
+        <v>47</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -25832,10 +26221,8 @@
           <t>622908********5480</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr">
-        <is>
-          <t>세종특별자치시 성북구***</t>
-        </is>
+      <c r="K411" t="s">
+        <v>48</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -26452,10 +26839,8 @@
           <t>622908********6587</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>河北省辛集县***</t>
-        </is>
+      <c r="K421" t="s">
+        <v>49</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -27320,10 +27705,8 @@
           <t>622908********7981</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K435" t="s">
+        <v>50</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
@@ -28002,10 +28385,8 @@
           <t>622908********9086</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K446" t="s">
+        <v>51</v>
       </c>
       <c r="L446" t="inlineStr">
         <is>
@@ -28126,10 +28507,8 @@
           <t>622908********9284</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K448" t="s">
+        <v>52</v>
       </c>
       <c r="L448" t="inlineStr">
         <is>
@@ -28808,10 +29187,8 @@
           <t>622908********0381</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K459" t="s">
+        <v>53</v>
       </c>
       <c r="L459" t="inlineStr">
         <is>
@@ -28932,10 +29309,8 @@
           <t>622908********0589</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K461" t="s">
+        <v>54</v>
       </c>
       <c r="L461" t="inlineStr">
         <is>
@@ -29056,10 +29431,8 @@
           <t>622908********0787</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K463" t="s">
+        <v>55</v>
       </c>
       <c r="L463" t="inlineStr">
         <is>
@@ -29552,10 +29925,8 @@
           <t>622908********1587</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K471" t="s">
+        <v>56</v>
       </c>
       <c r="L471" t="inlineStr">
         <is>
@@ -30668,10 +31039,8 @@
           <t>622908********3385</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr">
-        <is>
-          <t>熊本県神津島村***</t>
-        </is>
+      <c r="K489" t="s">
+        <v>57</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -30730,10 +31099,8 @@
           <t>622908********3484</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K490" t="s">
+        <v>58</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
@@ -31164,10 +31531,8 @@
           <t>622908********4186</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr">
-        <is>
-          <t>广西壮族自治区兴安盟县***</t>
-        </is>
+      <c r="K497" t="s">
+        <v>59</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -33272,10 +33637,8 @@
           <t>622908********7585</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K531" t="s">
+        <v>60</v>
       </c>
       <c r="L531" t="inlineStr">
         <is>
@@ -33582,10 +33945,8 @@
           <t>622908********8088</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K536" t="s">
+        <v>61</v>
       </c>
       <c r="L536" t="inlineStr">
         <is>
@@ -33644,10 +34005,8 @@
           <t>622908********8187</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K537" t="s">
+        <v>62</v>
       </c>
       <c r="L537" t="inlineStr">
         <is>
@@ -33954,10 +34313,8 @@
           <t>622908********8682</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr">
-        <is>
-          <t>福井県渋谷区***</t>
-        </is>
+      <c r="K542" t="s">
+        <v>63</v>
       </c>
       <c r="L542" t="inlineStr">
         <is>
@@ -34078,10 +34435,8 @@
           <t>622908********8880</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K544" t="s">
+        <v>64</v>
       </c>
       <c r="L544" t="inlineStr">
         <is>
@@ -34512,10 +34867,8 @@
           <t>622908********9581</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr">
-        <is>
-          <t>湖北省兴安盟县***</t>
-        </is>
+      <c r="K551" t="s">
+        <v>10</v>
       </c>
       <c r="L551" t="inlineStr">
         <is>
@@ -35132,10 +35485,8 @@
           <t>622908********0589</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K561" t="s">
+        <v>65</v>
       </c>
       <c r="L561" t="inlineStr">
         <is>
@@ -36062,10 +36413,8 @@
           <t>622908********2080</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K576" t="s">
+        <v>66</v>
       </c>
       <c r="L576" t="inlineStr">
         <is>
@@ -36186,10 +36535,8 @@
           <t>622908********2288</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K578" t="s">
+        <v>67</v>
       </c>
       <c r="L578" t="inlineStr">
         <is>
@@ -36310,10 +36657,8 @@
           <t>622908********2486</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K580" t="s">
+        <v>68</v>
       </c>
       <c r="L580" t="inlineStr">
         <is>
@@ -36930,10 +37275,8 @@
           <t>622908********3484</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr">
-        <is>
-          <t>天津市深圳县吉区***</t>
-        </is>
+      <c r="K590" t="s">
+        <v>69</v>
       </c>
       <c r="L590" t="inlineStr">
         <is>
@@ -37612,10 +37955,8 @@
           <t>622908********4581</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K601" t="s">
+        <v>70</v>
       </c>
       <c r="L601" t="inlineStr">
         <is>
@@ -37736,10 +38077,8 @@
           <t>622908********4789</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K603" t="s">
+        <v>71</v>
       </c>
       <c r="L603" t="inlineStr">
         <is>
@@ -37922,10 +38261,8 @@
           <t>622908********5083</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K606" t="s">
+        <v>72</v>
       </c>
       <c r="L606" t="inlineStr">
         <is>
@@ -38046,10 +38383,8 @@
           <t>622908********5281</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr">
-        <is>
-          <t>栃木県横浜市中区***</t>
-        </is>
+      <c r="K608" t="s">
+        <v>73</v>
       </c>
       <c r="L608" t="inlineStr">
         <is>
@@ -38356,10 +38691,8 @@
           <t>622908********5786</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K613" t="s">
+        <v>74</v>
       </c>
       <c r="L613" t="inlineStr">
         <is>
@@ -38790,10 +39123,8 @@
           <t>622908********6487</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr">
-        <is>
-          <t>广西壮族自治区兴安盟县***</t>
-        </is>
+      <c r="K620" t="s">
+        <v>59</v>
       </c>
       <c r="L620" t="inlineStr">
         <is>
@@ -39286,10 +39617,8 @@
           <t>622908********7287</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr">
-        <is>
-          <t>세종특별자치시 관악구***</t>
-        </is>
+      <c r="K628" t="s">
+        <v>75</v>
       </c>
       <c r="L628" t="inlineStr">
         <is>
@@ -41518,10 +41847,8 @@
           <t>622908********0885</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr">
-        <is>
-          <t>和歌山県川崎市宮前区***</t>
-        </is>
+      <c r="K664" t="s">
+        <v>76</v>
       </c>
       <c r="L664" t="inlineStr">
         <is>
@@ -41766,10 +42093,8 @@
           <t>622908********1289</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K668" t="s">
+        <v>77</v>
       </c>
       <c r="L668" t="inlineStr">
         <is>
@@ -42014,10 +42339,8 @@
           <t>622908********1685</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K672" t="s">
+        <v>66</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
@@ -42076,10 +42399,8 @@
           <t>622908********1784</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K673" t="s">
+        <v>78</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -42200,10 +42521,8 @@
           <t>622908********1982</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr">
-        <is>
-          <t>熊本県川崎市高津区***</t>
-        </is>
+      <c r="K675" t="s">
+        <v>79</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -43378,10 +43697,8 @@
           <t>622908********3889</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K694" t="s">
+        <v>80</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
@@ -43502,10 +43819,8 @@
           <t>622908********4085</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K696" t="s">
+        <v>81</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
@@ -44308,10 +44623,8 @@
           <t>622908********5488</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K709" t="s">
+        <v>82</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
@@ -44494,10 +44807,8 @@
           <t>622908********5785</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr">
-        <is>
-          <t>福井県印旛郡酒々井町横***</t>
-        </is>
+      <c r="K712" t="s">
+        <v>63</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -44804,10 +45115,8 @@
           <t>622908********6288</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K717" t="s">
+        <v>83</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
@@ -44866,10 +45175,8 @@
           <t>622908********6387</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K718" t="s">
+        <v>84</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
@@ -45052,10 +45359,8 @@
           <t>622908********6684</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K721" t="s">
+        <v>85</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
@@ -45176,10 +45481,8 @@
           <t>622908********6882</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K723" t="s">
+        <v>86</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
@@ -45238,10 +45541,8 @@
           <t>622908********6981</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K724" t="s">
+        <v>87</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -45300,10 +45601,8 @@
           <t>622908********7088</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K725" t="s">
+        <v>88</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
@@ -45362,10 +45661,8 @@
           <t>622908********7187</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K726" t="s">
+        <v>89</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
@@ -46416,10 +46713,8 @@
           <t>622908********8987</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K743" t="s">
+        <v>90</v>
       </c>
       <c r="L743" t="inlineStr">
         <is>
@@ -46602,10 +46897,8 @@
           <t>622908********9282</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K746" t="s">
+        <v>91</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -46788,10 +47081,8 @@
           <t>622908********9688</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K749" t="s">
+        <v>92</v>
       </c>
       <c r="L749" t="inlineStr">
         <is>
@@ -47408,10 +47699,8 @@
           <t>622908********0686</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K759" t="s">
+        <v>93</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -48028,10 +48317,8 @@
           <t>622908********1684</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K769" t="s">
+        <v>94</v>
       </c>
       <c r="L769" t="inlineStr">
         <is>
@@ -48462,10 +48749,8 @@
           <t>622908********2385</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K776" t="s">
+        <v>95</v>
       </c>
       <c r="L776" t="inlineStr">
         <is>
@@ -49082,10 +49367,8 @@
           <t>622908********3383</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K786" t="s">
+        <v>96</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -49206,10 +49489,8 @@
           <t>622908********3581</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K788" t="s">
+        <v>97</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -49826,10 +50107,8 @@
           <t>622908********4589</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K798" t="s">
+        <v>98</v>
       </c>
       <c r="L798" t="inlineStr">
         <is>
@@ -50260,10 +50539,8 @@
           <t>622908********5289</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K805" t="s">
+        <v>99</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -51314,10 +51591,8 @@
           <t>622908********7186</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K822" t="s">
+        <v>100</v>
       </c>
       <c r="L822" t="inlineStr">
         <is>
@@ -51810,10 +52085,8 @@
           <t>622908********7988</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K830" t="s">
+        <v>101</v>
       </c>
       <c r="L830" t="inlineStr">
         <is>
@@ -52244,10 +52517,8 @@
           <t>622908********8689</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K837" t="s">
+        <v>102</v>
       </c>
       <c r="L837" t="inlineStr">
         <is>
@@ -52616,10 +52887,8 @@
           <t>622908********9281</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K843" t="s">
+        <v>103</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -53546,10 +53815,8 @@
           <t>622908********0982</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K858" t="s">
+        <v>104</v>
       </c>
       <c r="L858" t="inlineStr">
         <is>
@@ -54104,10 +54371,8 @@
           <t>622908********1881</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K867" t="s">
+        <v>105</v>
       </c>
       <c r="L867" t="inlineStr">
         <is>
@@ -54662,10 +54927,8 @@
           <t>622908********2988</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K876" t="s">
+        <v>106</v>
       </c>
       <c r="L876" t="inlineStr">
         <is>
@@ -55034,10 +55297,8 @@
           <t>622908********3689</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K882" t="s">
+        <v>107</v>
       </c>
       <c r="L882" t="inlineStr">
         <is>
@@ -55158,10 +55419,8 @@
           <t>622908********3887</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K884" t="s">
+        <v>108</v>
       </c>
       <c r="L884" t="inlineStr">
         <is>
@@ -56460,10 +56719,8 @@
           <t>622908********5981</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K905" t="s">
+        <v>109</v>
       </c>
       <c r="L905" t="inlineStr">
         <is>
@@ -56522,10 +56779,8 @@
           <t>622908********6088</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K906" t="s">
+        <v>110</v>
       </c>
       <c r="L906" t="inlineStr">
         <is>
@@ -56956,10 +57211,8 @@
           <t>622908********6781</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr">
-        <is>
-          <t>河南省齐齐哈尔县吉区***</t>
-        </is>
+      <c r="K913" t="s">
+        <v>111</v>
       </c>
       <c r="L913" t="inlineStr">
         <is>
@@ -57018,10 +57271,8 @@
           <t>622908********6880</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr">
-        <is>
-          <t>湖北省呼和浩特县吉区***</t>
-        </is>
+      <c r="K914" t="s">
+        <v>112</v>
       </c>
       <c r="L914" t="inlineStr">
         <is>
@@ -57452,10 +57703,8 @@
           <t>622908********7581</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K921" t="s">
+        <v>113</v>
       </c>
       <c r="L921" t="inlineStr">
         <is>
@@ -57700,10 +57949,8 @@
           <t>622908********8084</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K925" t="s">
+        <v>114</v>
       </c>
       <c r="L925" t="inlineStr">
         <is>
@@ -58010,10 +58257,8 @@
           <t>622908********8589</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K930" t="s">
+        <v>115</v>
       </c>
       <c r="L930" t="inlineStr">
         <is>
@@ -58072,10 +58317,8 @@
           <t>622908********8688</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K931" t="s">
+        <v>116</v>
       </c>
       <c r="L931" t="inlineStr">
         <is>
@@ -58568,10 +58811,8 @@
           <t>622908********9488</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K939" t="s">
+        <v>117</v>
       </c>
       <c r="L939" t="inlineStr">
         <is>
@@ -58940,10 +59181,8 @@
           <t>622908********0080</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K945" t="s">
+        <v>118</v>
       </c>
       <c r="L945" t="inlineStr">
         <is>
@@ -59312,10 +59551,8 @@
           <t>622908********0684</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K951" t="s">
+        <v>119</v>
       </c>
       <c r="L951" t="inlineStr">
         <is>
@@ -59560,10 +59797,8 @@
           <t>622908********1088</t>
         </is>
       </c>
-      <c r="K955" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K955" t="s">
+        <v>120</v>
       </c>
       <c r="L955" t="inlineStr">
         <is>
@@ -59808,10 +60043,8 @@
           <t>622908********1484</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K959" t="s">
+        <v>121</v>
       </c>
       <c r="L959" t="inlineStr">
         <is>
@@ -60800,10 +61033,8 @@
           <t>622908********3084</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K975" t="s">
+        <v>122</v>
       </c>
       <c r="L975" t="inlineStr">
         <is>
@@ -62660,10 +62891,8 @@
           <t>622908********6180</t>
         </is>
       </c>
-      <c r="K1005" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K1005" t="s">
+        <v>123</v>
       </c>
       <c r="L1005" t="inlineStr">
         <is>
@@ -63838,10 +64067,8 @@
           <t>622908********8087</t>
         </is>
       </c>
-      <c r="K1024" t="inlineStr">
-        <is>
-          <t>辽宁省济南县吉区***</t>
-        </is>
+      <c r="K1024" t="s">
+        <v>124</v>
       </c>
       <c r="L1024" t="inlineStr">
         <is>
@@ -64086,10 +64313,8 @@
           <t>622908********8483</t>
         </is>
       </c>
-      <c r="K1028" t="inlineStr">
-        <is>
-          <t>沖縄県品川区***</t>
-        </is>
+      <c r="K1028" t="s">
+        <v>125</v>
       </c>
       <c r="L1028" t="inlineStr">
         <is>
@@ -64148,10 +64373,8 @@
           <t>622908********8582</t>
         </is>
       </c>
-      <c r="K1029" t="inlineStr">
-        <is>
-          <t>河北省西宁县***</t>
-        </is>
+      <c r="K1029" t="s">
+        <v>126</v>
       </c>
       <c r="L1029" t="inlineStr">
         <is>
@@ -64334,10 +64557,8 @@
           <t>622908********8889</t>
         </is>
       </c>
-      <c r="K1032" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K1032" t="s">
+        <v>127</v>
       </c>
       <c r="L1032" t="inlineStr">
         <is>
@@ -66132,10 +66353,8 @@
           <t>622908********1883</t>
         </is>
       </c>
-      <c r="K1061" t="inlineStr">
-        <is>
-          <t>河北省齐齐哈尔县***</t>
-        </is>
+      <c r="K1061" t="s">
+        <v>128</v>
       </c>
       <c r="L1061" t="inlineStr">
         <is>
@@ -66194,10 +66413,8 @@
           <t>622908********1982</t>
         </is>
       </c>
-      <c r="K1062" t="inlineStr">
-        <is>
-          <t>澳门特别行政区***</t>
-        </is>
+      <c r="K1062" t="s">
+        <v>62</v>
       </c>
       <c r="L1062" t="inlineStr">
         <is>
@@ -66442,10 +66659,8 @@
           <t>622908********2386</t>
         </is>
       </c>
-      <c r="K1066" t="inlineStr">
-        <is>
-          <t>佐賀県横浜市鶴見区***</t>
-        </is>
+      <c r="K1066" t="s">
+        <v>129</v>
       </c>
       <c r="L1066" t="inlineStr">
         <is>
@@ -67124,10 +67339,8 @@
           <t>622908********3483</t>
         </is>
       </c>
-      <c r="K1077" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K1077" t="s">
+        <v>130</v>
       </c>
       <c r="L1077" t="inlineStr">
         <is>
@@ -67186,10 +67399,8 @@
           <t>622908********3582</t>
         </is>
       </c>
-      <c r="K1078" t="inlineStr">
-        <is>
-          <t>澳门特别行政区佛山县吉区***</t>
-        </is>
+      <c r="K1078" t="s">
+        <v>131</v>
       </c>
       <c r="L1078" t="inlineStr">
         <is>
@@ -67620,10 +67831,8 @@
           <t>622908********4283</t>
         </is>
       </c>
-      <c r="K1085" t="inlineStr">
-        <is>
-          <t>台湾省惠州县吉区***</t>
-        </is>
+      <c r="K1085" t="s">
+        <v>132</v>
       </c>
       <c r="L1085" t="inlineStr">
         <is>
@@ -67682,10 +67891,8 @@
           <t>622908********4382</t>
         </is>
       </c>
-      <c r="K1086" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K1086" t="s">
+        <v>71</v>
       </c>
       <c r="L1086" t="inlineStr">
         <is>
@@ -67868,10 +68075,8 @@
           <t>622908********4689</t>
         </is>
       </c>
-      <c r="K1089" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K1089" t="s">
+        <v>133</v>
       </c>
       <c r="L1089" t="inlineStr">
         <is>
@@ -68054,10 +68259,8 @@
           <t>622908********4986</t>
         </is>
       </c>
-      <c r="K1092" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K1092" t="s">
+        <v>134</v>
       </c>
       <c r="L1092" t="inlineStr">
         <is>
@@ -69294,10 +69497,8 @@
           <t>622908********6981</t>
         </is>
       </c>
-      <c r="K1112" t="inlineStr">
-        <is>
-          <t>栃木県中央区***</t>
-        </is>
+      <c r="K1112" t="s">
+        <v>135</v>
       </c>
       <c r="L1112" t="inlineStr">
         <is>
@@ -70596,10 +70797,8 @@
           <t>622908********9084</t>
         </is>
       </c>
-      <c r="K1133" t="inlineStr">
-        <is>
-          <t>세종특별자치시 구로구***</t>
-        </is>
+      <c r="K1133" t="s">
+        <v>136</v>
       </c>
       <c r="L1133" t="inlineStr">
         <is>
@@ -70658,10 +70857,8 @@
           <t>622908********9183</t>
         </is>
       </c>
-      <c r="K1134" t="inlineStr">
-        <is>
-          <t>天津市沈阳县吉区***</t>
-        </is>
+      <c r="K1134" t="s">
+        <v>137</v>
       </c>
       <c r="L1134" t="inlineStr">
         <is>
@@ -70782,10 +70979,8 @@
           <t>622908********9381</t>
         </is>
       </c>
-      <c r="K1136" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K1136" t="s">
+        <v>138</v>
       </c>
       <c r="L1136" t="inlineStr">
         <is>
@@ -71464,10 +71659,8 @@
           <t>622908********0488</t>
         </is>
       </c>
-      <c r="K1147" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K1147" t="s">
+        <v>139</v>
       </c>
       <c r="L1147" t="inlineStr">
         <is>
@@ -71774,10 +71967,8 @@
           <t>622908********0983</t>
         </is>
       </c>
-      <c r="K1152" t="inlineStr">
-        <is>
-          <t>吉林省丹县吉区***</t>
-        </is>
+      <c r="K1152" t="s">
+        <v>140</v>
       </c>
       <c r="L1152" t="inlineStr">
         <is>
@@ -72022,10 +72213,8 @@
           <t>622908********1486</t>
         </is>
       </c>
-      <c r="K1156" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K1156" t="s">
+        <v>141</v>
       </c>
       <c r="L1156" t="inlineStr">
         <is>
@@ -72456,10 +72645,8 @@
           <t>622908********2187</t>
         </is>
       </c>
-      <c r="K1163" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K1163" t="s">
+        <v>142</v>
       </c>
       <c r="L1163" t="inlineStr">
         <is>
@@ -72518,10 +72705,8 @@
           <t>622908********2286</t>
         </is>
       </c>
-      <c r="K1164" t="inlineStr">
-        <is>
-          <t>青海省成都县***</t>
-        </is>
+      <c r="K1164" t="s">
+        <v>143</v>
       </c>
       <c r="L1164" t="inlineStr">
         <is>
@@ -72642,10 +72827,8 @@
           <t>622908********2484</t>
         </is>
       </c>
-      <c r="K1166" t="inlineStr">
-        <is>
-          <t>湖北省辽阳县***</t>
-        </is>
+      <c r="K1166" t="s">
+        <v>144</v>
       </c>
       <c r="L1166" t="inlineStr">
         <is>
@@ -72766,10 +72949,8 @@
           <t>622908********2682</t>
         </is>
       </c>
-      <c r="K1168" t="inlineStr">
-        <is>
-          <t>山梨県横浜市鶴見区***</t>
-        </is>
+      <c r="K1168" t="s">
+        <v>145</v>
       </c>
       <c r="L1168" t="inlineStr">
         <is>
@@ -72890,10 +73071,8 @@
           <t>622908********2880</t>
         </is>
       </c>
-      <c r="K1170" t="inlineStr">
-        <is>
-          <t>广东省宁德县***</t>
-        </is>
+      <c r="K1170" t="s">
+        <v>146</v>
       </c>
       <c r="L1170" t="inlineStr">
         <is>
@@ -72952,10 +73131,8 @@
           <t>622908********2989</t>
         </is>
       </c>
-      <c r="K1171" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K1171" t="s">
+        <v>147</v>
       </c>
       <c r="L1171" t="inlineStr">
         <is>
@@ -74006,10 +74183,8 @@
           <t>622908********4787</t>
         </is>
       </c>
-      <c r="K1188" t="inlineStr">
-        <is>
-          <t>福井県横浜市磯子区***</t>
-        </is>
+      <c r="K1188" t="s">
+        <v>148</v>
       </c>
       <c r="L1188" t="inlineStr">
         <is>
@@ -75060,10 +75235,8 @@
           <t>622908********6485</t>
         </is>
       </c>
-      <c r="K1205" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K1205" t="s">
+        <v>149</v>
       </c>
       <c r="L1205" t="inlineStr">
         <is>
@@ -75432,10 +75605,8 @@
           <t>622908********7087</t>
         </is>
       </c>
-      <c r="K1211" t="inlineStr">
-        <is>
-          <t>甘肃省桂珍县***</t>
-        </is>
+      <c r="K1211" t="s">
+        <v>150</v>
       </c>
       <c r="L1211" t="inlineStr">
         <is>
@@ -75680,10 +75851,8 @@
           <t>622908********7483</t>
         </is>
       </c>
-      <c r="K1215" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K1215" t="s">
+        <v>151</v>
       </c>
       <c r="L1215" t="inlineStr">
         <is>
@@ -75804,10 +75973,8 @@
           <t>622908********7681</t>
         </is>
       </c>
-      <c r="K1217" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K1217" t="s">
+        <v>71</v>
       </c>
       <c r="L1217" t="inlineStr">
         <is>
@@ -76362,10 +76529,8 @@
           <t>622908********8580</t>
         </is>
       </c>
-      <c r="K1226" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K1226" t="s">
+        <v>152</v>
       </c>
       <c r="L1226" t="inlineStr">
         <is>
@@ -76424,10 +76589,8 @@
           <t>622908********8689</t>
         </is>
       </c>
-      <c r="K1227" t="inlineStr">
-        <is>
-          <t>广西壮族自治区***</t>
-        </is>
+      <c r="K1227" t="s">
+        <v>153</v>
       </c>
       <c r="L1227" t="inlineStr">
         <is>
@@ -76486,10 +76649,8 @@
           <t>622908********8788</t>
         </is>
       </c>
-      <c r="K1228" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区***</t>
-        </is>
+      <c r="K1228" t="s">
+        <v>154</v>
       </c>
       <c r="L1228" t="inlineStr">
         <is>
@@ -77044,10 +77205,8 @@
           <t>622908********9687</t>
         </is>
       </c>
-      <c r="K1237" t="inlineStr">
-        <is>
-          <t>内蒙古自治区***</t>
-        </is>
+      <c r="K1237" t="s">
+        <v>155</v>
       </c>
       <c r="L1237" t="inlineStr">
         <is>
@@ -77168,10 +77327,8 @@
           <t>622908********9885</t>
         </is>
       </c>
-      <c r="K1239" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K1239" t="s">
+        <v>80</v>
       </c>
       <c r="L1239" t="inlineStr">
         <is>
@@ -77478,10 +77635,8 @@
           <t>622908********0388</t>
         </is>
       </c>
-      <c r="K1244" t="inlineStr">
-        <is>
-          <t>栃木県印旛郡印旛村***</t>
-        </is>
+      <c r="K1244" t="s">
+        <v>135</v>
       </c>
       <c r="L1244" t="inlineStr">
         <is>
@@ -79710,10 +79865,8 @@
           <t>622908********3986</t>
         </is>
       </c>
-      <c r="K1280" t="inlineStr">
-        <is>
-          <t>西藏自治区***</t>
-        </is>
+      <c r="K1280" t="s">
+        <v>156</v>
       </c>
       <c r="L1280" t="inlineStr">
         <is>
@@ -80640,10 +80793,8 @@
           <t>622908********5486</t>
         </is>
       </c>
-      <c r="K1295" t="inlineStr">
-        <is>
-          <t>云南省兴安盟县***</t>
-        </is>
+      <c r="K1295" t="s">
+        <v>157</v>
       </c>
       <c r="L1295" t="inlineStr">
         <is>
@@ -81446,10 +81597,8 @@
           <t>622908********6781</t>
         </is>
       </c>
-      <c r="K1308" t="inlineStr">
-        <is>
-          <t>香港特别行政区***</t>
-        </is>
+      <c r="K1308" t="s">
+        <v>158</v>
       </c>
       <c r="L1308" t="inlineStr">
         <is>
@@ -81880,10 +82029,8 @@
           <t>622908********7482</t>
         </is>
       </c>
-      <c r="K1315" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K1315" t="s">
+        <v>159</v>
       </c>
       <c r="L1315" t="inlineStr">
         <is>
@@ -83616,10 +83763,8 @@
           <t>622908********0286</t>
         </is>
       </c>
-      <c r="K1343" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区***</t>
-        </is>
+      <c r="K1343" t="s">
+        <v>160</v>
       </c>
       <c r="L1343" t="inlineStr">
         <is>
